--- a/data/obx_xlsx/BNOR.OL.xlsx
+++ b/data/obx_xlsx/BNOR.OL.xlsx
@@ -3513,10 +3513,12 @@
         <v>1.0</v>
       </c>
       <c r="L40" s="17">
-        <v>2.0</v>
+        <f t="shared" ref="L40:M40" si="1">L41</f>
+        <v>71</v>
       </c>
       <c r="M40" s="17">
-        <v>6.0</v>
+        <f t="shared" si="1"/>
+        <v>407</v>
       </c>
       <c r="N40" s="16">
         <v>319.0</v>

--- a/data/obx_xlsx/BNOR.OL.xlsx
+++ b/data/obx_xlsx/BNOR.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="516">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -936,7 +936,7 @@
     <t>Convertible bond loan</t>
   </si>
   <si>
-    <t>Bond loan</t>
+    <t>Bond loan (Do not use)</t>
   </si>
   <si>
     <t>Reported Total Long Term Debt</t>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>Derivative Liabilities</t>
+  </si>
+  <si>
+    <t>Reserve-based lending facility (Do not use)</t>
   </si>
   <si>
     <t>Pension provisions</t>
@@ -11013,8 +11016,14 @@
       <c r="Q31" s="16">
         <v>892.48</v>
       </c>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
+      <c r="R31" s="15">
+        <f t="shared" ref="R31:S31" si="1">SUM(R33:R34)</f>
+        <v>659.82</v>
+      </c>
+      <c r="S31" s="15">
+        <f t="shared" si="1"/>
+        <v>867.35</v>
+      </c>
       <c r="T31" s="16">
         <v>973.66</v>
       </c>
@@ -12307,13 +12316,16 @@
       <c r="S67" s="16">
         <v>4456.75</v>
       </c>
-      <c r="T67" s="17">
-        <v>6.65</v>
+      <c r="T67" s="16">
+        <v>2843.71</v>
       </c>
       <c r="U67" s="16">
         <v>1803.51</v>
       </c>
-      <c r="V67" s="15"/>
+      <c r="V67" s="15">
+        <f>SUM(V82,V66)</f>
+        <v>1.25</v>
+      </c>
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
@@ -14450,7 +14462,7 @@
       <c r="V118" s="15"/>
     </row>
     <row r="119" ht="15.0" customHeight="1">
-      <c r="A119" s="14" t="s">
+      <c r="A119" s="22" t="s">
         <v>305</v>
       </c>
       <c r="B119" s="16">
@@ -14702,8 +14714,8 @@
       <c r="V124" s="15"/>
     </row>
     <row r="125" ht="15.0" customHeight="1">
-      <c r="A125" s="14" t="s">
-        <v>301</v>
+      <c r="A125" s="22" t="s">
+        <v>311</v>
       </c>
       <c r="B125" s="16">
         <v>7679.89</v>
@@ -14743,7 +14755,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -14785,7 +14797,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B127" s="15">
         <v>13519.03</v>
@@ -14845,7 +14857,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B128" s="17">
         <v>17.1</v>
@@ -14885,7 +14897,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
@@ -14919,7 +14931,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B130" s="23">
         <v>-1.01</v>
@@ -14963,7 +14975,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B131" s="19">
         <v>24288.98</v>
@@ -15031,7 +15043,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B132" s="15"/>
       <c r="C132" s="23">
@@ -15067,7 +15079,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="18" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B133" s="19">
         <v>25807.86</v>
@@ -15135,7 +15147,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B134" s="17">
         <v>16.09</v>
@@ -15203,7 +15215,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B135" s="16">
         <v>7565.22</v>
@@ -15267,7 +15279,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="16">
@@ -15307,7 +15319,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B137" s="15"/>
       <c r="C137" s="15">
@@ -15341,7 +15353,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="23">
@@ -15391,7 +15403,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B139" s="15"/>
       <c r="C139" s="24">
@@ -15429,7 +15441,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B140" s="15"/>
       <c r="C140" s="24">
@@ -15473,7 +15485,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B141" s="15"/>
       <c r="C141" s="23">
@@ -15505,7 +15517,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B142" s="15"/>
       <c r="C142" s="15"/>
@@ -15535,7 +15547,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
@@ -15565,7 +15577,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B144" s="15"/>
       <c r="C144" s="15"/>
@@ -15597,7 +15609,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B145" s="20">
         <v>7581.32</v>
@@ -15665,7 +15677,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B146" s="20">
         <v>7581.32</v>
@@ -15733,7 +15745,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B147" s="15"/>
       <c r="C147" s="17">
@@ -15765,7 +15777,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B148" s="19">
         <v>33389.18</v>
@@ -15833,7 +15845,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B149" s="17">
         <v>25.57</v>
@@ -15901,7 +15913,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="15">
         <v>0.0</v>
@@ -15969,7 +15981,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B151" s="17">
         <v>25.57</v>
@@ -16037,7 +16049,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -16067,7 +16079,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -16097,7 +16109,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -16125,7 +16137,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -16153,7 +16165,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B156" s="15"/>
       <c r="C156" s="15"/>
@@ -16183,7 +16195,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -16213,7 +16225,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
@@ -16243,7 +16255,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
@@ -16273,7 +16285,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15"/>
@@ -16303,7 +16315,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -16333,7 +16345,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -16361,7 +16373,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -16389,7 +16401,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B164" s="17">
         <v>25.57</v>
@@ -16457,7 +16469,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B165" s="15">
         <v>0.0</v>
@@ -16525,7 +16537,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B166" s="17">
         <v>1.0</v>
@@ -16593,7 +16605,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B167" s="17">
         <v>25.57</v>
@@ -16661,7 +16673,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B168" s="17">
         <v>53.0</v>
@@ -16721,7 +16733,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
@@ -16755,7 +16767,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
@@ -16789,7 +16801,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
@@ -16823,7 +16835,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
@@ -16857,7 +16869,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
@@ -16885,7 +16897,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -16917,7 +16929,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -16951,7 +16963,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="16">
@@ -17845,7 +17857,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18218,67 +18230,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -18323,7 +18335,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -18485,7 +18497,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B21" s="17">
         <v>62.24</v>
@@ -18543,7 +18555,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -18613,7 +18625,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="16">
@@ -18651,7 +18663,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B25" s="16">
         <v>2585.87</v>
@@ -18731,7 +18743,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -18759,7 +18771,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -18797,7 +18809,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -18835,7 +18847,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B30" s="17">
         <v>10.37</v>
@@ -18891,7 +18903,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -18933,7 +18945,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -18967,7 +18979,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -18997,7 +19009,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -19033,7 +19045,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -19065,7 +19077,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -19115,7 +19127,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -19151,7 +19163,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -19185,7 +19197,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -19219,7 +19231,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -19273,7 +19285,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -19305,7 +19317,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -19335,7 +19347,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -19367,7 +19379,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -19407,7 +19419,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -19485,7 +19497,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -19521,7 +19533,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
@@ -19549,7 +19561,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -19609,7 +19621,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B51" s="17">
         <v>86.09</v>
@@ -19641,7 +19653,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B52" s="23">
         <v>-31.12</v>
@@ -19673,7 +19685,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B53" s="24">
         <v>-544.56</v>
@@ -19741,7 +19753,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" s="24">
         <v>-144.18</v>
@@ -19809,7 +19821,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -19841,7 +19853,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -19877,7 +19889,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -19905,7 +19917,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" s="24">
         <v>-125.51</v>
@@ -19985,7 +19997,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B60" s="24">
         <v>-128.62</v>
@@ -20025,7 +20037,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B61" s="17">
         <v>18.67</v>
@@ -20087,7 +20099,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -20129,7 +20141,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B63" s="24">
         <v>-215.75</v>
@@ -20185,7 +20197,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="18" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B64" s="20">
         <v>4320.16</v>
@@ -20253,7 +20265,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -20283,7 +20295,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -20311,7 +20323,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B67" s="15"/>
       <c r="C67" s="17">
@@ -20339,7 +20351,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -20369,7 +20381,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -20401,7 +20413,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -20437,7 +20449,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -20467,7 +20479,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -20499,7 +20511,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -20527,7 +20539,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B74" s="23">
         <v>-46.68</v>
@@ -20563,7 +20575,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B75" s="24">
         <v>-440.83</v>
@@ -20603,7 +20615,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15">
@@ -20641,7 +20653,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B77" s="16">
         <v>1643.01</v>
@@ -20677,7 +20689,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B78" s="23">
         <v>-22.82</v>
@@ -20705,7 +20717,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -20735,7 +20747,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -20763,7 +20775,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -20795,7 +20807,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
@@ -20843,7 +20855,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
@@ -20893,7 +20905,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -20923,7 +20935,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -20961,7 +20973,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -20989,7 +21001,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
@@ -21017,7 +21029,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -21051,7 +21063,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B89" s="17">
         <v>1.04</v>
@@ -21085,7 +21097,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B90" s="20">
         <v>1133.72</v>
@@ -21153,7 +21165,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B91" s="24">
         <v>-4474.71</v>
@@ -21197,7 +21209,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -21225,7 +21237,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
@@ -21255,7 +21267,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B94" s="23">
         <v>-6.22</v>
@@ -21295,7 +21307,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B95" s="24">
         <v>-518.63</v>
@@ -21329,7 +21341,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B96" s="15"/>
       <c r="C96" s="17">
@@ -21393,7 +21405,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B97" s="16">
         <v>2964.47</v>
@@ -21421,7 +21433,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -21453,7 +21465,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -21483,7 +21495,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B100" s="16">
         <v>207.45</v>
@@ -21515,7 +21527,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -21553,7 +21565,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B102" s="24">
         <v>-1207.36</v>
@@ -21617,7 +21629,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
@@ -21651,7 +21663,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -21689,7 +21701,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B105" s="24">
         <v>-3537.04</v>
@@ -21717,7 +21729,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -21761,7 +21773,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -21803,7 +21815,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B108" s="15"/>
       <c r="C108" s="15"/>
@@ -21837,7 +21849,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -21867,7 +21879,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
@@ -21907,7 +21919,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
@@ -21955,7 +21967,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
@@ -21993,7 +22005,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -22035,7 +22047,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -22069,7 +22081,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
@@ -22105,7 +22117,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -22147,7 +22159,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="17">
@@ -22175,7 +22187,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B118" s="25">
         <v>-6572.04</v>
@@ -22243,7 +22255,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -22277,7 +22289,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B120" s="16">
         <v>2520.74</v>
@@ -22345,7 +22357,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B121" s="16">
         <v>1435.39</v>
@@ -22413,7 +22425,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
@@ -22451,7 +22463,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="18" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B123" s="25">
         <v>-1118.16</v>
@@ -22519,7 +22531,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -22551,7 +22563,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -22583,7 +22595,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -23513,7 +23525,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23972,7 +23984,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24062,7 +24074,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="29" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -24087,7 +24099,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B21" s="32">
         <v>26410.21</v>
@@ -24148,7 +24160,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="31" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B22" s="32">
         <v>19308.48</v>
@@ -24201,7 +24213,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -24226,7 +24238,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B24" s="32">
         <v>13677.21</v>
@@ -24287,7 +24299,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B25" s="33">
         <v>8369.22</v>
@@ -24340,7 +24352,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="29" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -24365,7 +24377,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B27" s="33">
         <v>516.15</v>
@@ -24426,7 +24438,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B28" s="33">
         <v>323.41</v>
@@ -24479,7 +24491,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -24504,7 +24516,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="31" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B30" s="35">
         <v>-3.75</v>
@@ -24565,7 +24577,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B31" s="35">
         <v>-4.21</v>
@@ -24618,7 +24630,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -24643,7 +24655,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B33" s="36">
         <v>0.0</v>
@@ -24704,7 +24716,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B34" s="36">
         <v>0.0</v>
@@ -24757,7 +24769,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B35" s="36">
         <v>0.0</v>
@@ -24818,7 +24830,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B36" s="36">
         <v>0.0</v>
@@ -24871,7 +24883,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="29" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -24896,7 +24908,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B38" s="34">
         <v>1.73</v>
@@ -24953,7 +24965,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B39" s="34">
         <v>1.1</v>
@@ -25004,7 +25016,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -25029,7 +25041,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="31" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B41" s="34">
         <v>2.19</v>
@@ -25078,7 +25090,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="31" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B42" s="34">
         <v>1.45</v>
@@ -25123,7 +25135,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -25148,7 +25160,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="31" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B44" s="34">
         <v>1.7</v>
@@ -25209,7 +25221,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="31" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B45" s="34">
         <v>1.05</v>
@@ -25262,7 +25274,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -25287,7 +25299,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="31" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B47" s="32"/>
       <c r="C47" s="32"/>
@@ -25328,7 +25340,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="31" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B48" s="32"/>
       <c r="C48" s="34">
@@ -25363,7 +25375,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="29" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
@@ -25388,7 +25400,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="31" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B50" s="34">
         <v>18.91</v>
@@ -25435,7 +25447,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="31" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B51" s="34">
         <v>5.94</v>
@@ -25478,7 +25490,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
@@ -25503,7 +25515,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B53" s="32"/>
       <c r="C53" s="34">
@@ -25538,7 +25550,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="34">
@@ -25573,7 +25585,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="29" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
@@ -25598,7 +25610,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="31" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B56" s="32"/>
       <c r="C56" s="34">
@@ -25639,7 +25651,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="31" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B57" s="34">
         <v>1.1</v>
@@ -25690,7 +25702,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="29" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
@@ -25715,7 +25727,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="31" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="34">
@@ -25750,7 +25762,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="31" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B60" s="32"/>
       <c r="C60" s="32"/>
@@ -25777,7 +25789,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -25802,7 +25814,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="31" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B62" s="34">
         <v>3.31</v>
@@ -25863,7 +25875,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="31" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B63" s="34">
         <v>2.36</v>
@@ -25916,7 +25928,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B64" s="30"/>
       <c r="C64" s="30"/>
@@ -25941,7 +25953,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="31" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B65" s="34">
         <v>6.44</v>
@@ -25992,7 +26004,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="31" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B66" s="34">
         <v>4.4</v>
@@ -26043,7 +26055,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B67" s="30"/>
       <c r="C67" s="30"/>
@@ -26068,7 +26080,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="31" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B68" s="34">
         <v>12.13</v>
@@ -26123,7 +26135,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="31" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B69" s="34">
         <v>7.69</v>
@@ -26176,7 +26188,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B70" s="30"/>
       <c r="C70" s="30"/>
@@ -26201,7 +26213,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="31" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B71" s="32"/>
       <c r="C71" s="32"/>
@@ -26244,7 +26256,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="31" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B72" s="32"/>
       <c r="C72" s="32"/>
